--- a/stories/arbres/ATOM-SAN.MOV.001-08.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Après le goûter, Bruno a les jambes qui bougent. Papa dit : on va dehors. Papa, c'est l'adulte. Ils ouvrent la porte du jardin. L'air est frais. L'herbe sent le vert. Bruno court jusqu'au ballon. Papa reste près de lui. Ils jouent dehors, avec un adulte. Bruno tape le ballon. Papa le renvoie. Les pieds tapent l'herbe. Bruno souffle. Il rit. Papa dit : encore un moment dehors. Bruno saute. Il touche les feuilles basses. Papa le voit. Ils jouent ensemble. Quand les joues de Bruno sont chaudes, papa dit : on rentre. Bruno range le ballon. Il a bougé dehors, avec un adulte.</t>
+          <t>Après le goûter, Bruno a les jambes qui bougent. On va dehors. Papa, c'est l'adulte. Ils ouvrent la porte du jardin. L'air est frais. L'herbe sent le vert. Bruno court jusqu'au ballon. Papa reste près de lui. Ils jouent dehors, avec un adulte. Bruno tape le ballon. Papa le renvoie. Les pieds tapent l'herbe. Bruno souffle. Il rit. Encore un moment dehors. Bruno saute. Il touche les feuilles basses. Papa le voit. Ils jouent ensemble. Quand les joues de Bruno sont chaudes, On rentre. Bruno range le ballon. Il a bougé dehors, avec un adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Après le goûter, Bruno a les jambes qui bougent.
+papa|On va dehors. Papa, c'est l'adulte. Ils ouvrent la porte du jardin. L'air est frais. L'herbe sent le vert.
+narrateur|Bruno court jusqu'au ballon. Papa reste près de lui. Ils jouent dehors, avec un adulte. Bruno tape le ballon. Papa le renvoie. Les pieds tapent l'herbe. Bruno souffle. Il rit.
+papa|Encore un moment dehors.
+narrateur|Bruno saute. Il touche les feuilles basses. Papa le voit. Ils jouent ensemble. Quand les joues de Bruno sont chaudes,
+papa|On rentre.
+narrateur|Bruno range le ballon. Il a bougé dehors, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Bruno veut bouger. Où joue-t-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Bruno a joué dehors. Papa, l'adulte, était avec lui. Les jambes ont bougé.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Bruno boit de l'eau. Il sent encore l'herbe sur ses chaussures.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.MOV.001-08.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-08.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Bruno range le ballon. Il a bougé dehors, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Bruno veut bouger. Où joue-t-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Bruno a joué dehors. Papa, l'adulte, était avec lui. Les jambes ont bougé.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1841,7 @@
           <t>narrateur|Bruno boit de l'eau. Il sent encore l'herbe sur ses chaussures.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2052,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2267,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.MOV.001-08.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bruno joue dehors avec papa</t>
+          <t>Les miettes et le ballon</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN.ALI.003</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Des miettes restent sur la table. Une mouche tourne autour du pot de confiture. La poignée du jardin est chaude. Raphaël et papa jouent au ballon dehors, avec un adulte.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Après le goûter, Bruno a les jambes qui bougent. On va dehors. Papa, c'est l'adulte. Ils ouvrent la porte du jardin. L'air est frais. L'herbe sent le vert. Bruno court jusqu'au ballon. Papa reste près de lui. Ils jouent dehors, avec un adulte. Bruno tape le ballon. Papa le renvoie. Les pieds tapent l'herbe. Bruno souffle. Il rit. Encore un moment dehors. Bruno saute. Il touche les feuilles basses. Papa le voit. Ils jouent ensemble. Quand les joues de Bruno sont chaudes, On rentre. Bruno range le ballon. Il a bougé dehors, avec un adulte.</t>
+          <t>Des miettes dorées restent sur la table. Le bois sent le gâteau. Une mouche tourne autour du pot. Le pot de confiture est collant. La poignée du jardin est chaude. Le soleil l'a touchée. Un rayon glisse sur le carrelage. Il est long, tout jaune. Raphaël vit ici, avec papa. Papa, la mouche tourne ! Oui. Elle aime le sucre. Tu as fini ton goûter ? Oui, papa. En ce moment, les jambes de Raphaël bougent. Sous la table, ses pieds tapent. Tes jambes veulent dehors ? Oui ! On va dehors, alors. On y va ensemble. On joue dehors, avec un adulte. Ils poussent la porte du jardin. L'air est frais, après le gâteau. L'herbe sent le vert. Ça sent l'herbe, papa. Oui. Tout vert. Un ballon rouge attend dans l'herbe. Il a une tache de soleil. Le ballon ! Il t'attendait. Raphaël court jusqu'au ballon. Papa reste près de lui. Je reste avec toi. Raphaël tape le ballon. Les pieds tapent l'herbe. Papa le renvoie. Bien tapé, Raphaël. Je joue dehors, avec un adulte. Oui. Bravo. Raphaël souffle un peu. Il rit. Encore un moment dehors ? Oui ! Raphaël saute. Il touche une feuille basse. La feuille est lisse et tiède. Tu vois la feuille ? Oui. Elle est douce. Ils jouent encore. Les joues de Raphaël deviennent chaudes. Tes joues sont chaudes. On rentre ? Oui, papa. Raphaël range le ballon près du bac. Une miette est encore collée à sa manche. Tu as bougé dehors, avec un adulte. Oui. Bravo. La poignée est encore chaude. Ils rentrent ensemble.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1329,76 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Après le goûter, Bruno a les jambes qui bougent.
-papa|On va dehors. Papa, c'est l'adulte. Ils ouvrent la porte du jardin. L'air est frais. L'herbe sent le vert.
-narrateur|Bruno court jusqu'au ballon. Papa reste près de lui. Ils jouent dehors, avec un adulte. Bruno tape le ballon. Papa le renvoie. Les pieds tapent l'herbe. Bruno souffle. Il rit.
-papa|Encore un moment dehors.
-narrateur|Bruno saute. Il touche les feuilles basses. Papa le voit. Ils jouent ensemble. Quand les joues de Bruno sont chaudes,
-papa|On rentre.
-narrateur|Bruno range le ballon. Il a bougé dehors, avec un adulte.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Des miettes dorées restent sur la table.
+narrateur|Le bois sent le gâteau.
+narrateur|Une mouche tourne autour du pot.
+narrateur|Le pot de confiture est collant.
+narrateur|La poignée du jardin est chaude.
+narrateur|Le soleil l'a touchée.
+narrateur|Un rayon glisse sur le carrelage.
+narrateur|Il est long, tout jaune.
+narrateur|Raphaël vit ici, avec papa.
+enfant-m|Papa, la mouche tourne !
+papa|Oui.
+papa|Elle aime le sucre.
+papa|Tu as fini ton goûter ?
+enfant-m|Oui, papa.
+narrateur|En ce moment, les jambes de Raphaël bougent.
+narrateur|Sous la table, ses pieds tapent.
+papa|Tes jambes veulent dehors ?
+enfant-m|Oui !
+papa|On va dehors, alors.
+papa|On y va ensemble.
+papa|On joue dehors, avec un adulte.
+narrateur|Ils poussent la porte du jardin.
+narrateur|L'air est frais, après le gâteau.
+narrateur|L'herbe sent le vert.
+enfant-m|Ça sent l'herbe, papa.
+papa|Oui.
+papa|Tout vert.
+narrateur|Un ballon rouge attend dans l'herbe.
+narrateur|Il a une tache de soleil.
+enfant-m|Le ballon !
+papa|Il t'attendait.
+narrateur|Raphaël court jusqu'au ballon.
+narrateur|Papa reste près de lui.
+papa|Je reste avec toi.
+narrateur|Raphaël tape le ballon.
+narrateur|Les pieds tapent l'herbe.
+narrateur|Papa le renvoie.
+papa|Bien tapé, Raphaël.
+enfant-m|Je joue dehors, avec un adulte.
+papa|Oui.
+papa|Bravo.
+narrateur|Raphaël souffle un peu.
+narrateur|Il rit.
+papa|Encore un moment dehors ?
+enfant-m|Oui !
+narrateur|Raphaël saute.
+narrateur|Il touche une feuille basse.
+narrateur|La feuille est lisse et tiède.
+papa|Tu vois la feuille ?
+enfant-m|Oui.
+enfant-m|Elle est douce.
+narrateur|Ils jouent encore.
+narrateur|Les joues de Raphaël deviennent chaudes.
+papa|Tes joues sont chaudes.
+papa|On rentre ?
+enfant-m|Oui, papa.
+narrateur|Raphaël range le ballon près du bac.
+narrateur|Une miette est encore collée à sa manche.
+papa|Tu as bougé dehors, avec un adulte.
+enfant-m|Oui.
+papa|Bravo.
+narrateur|La poignée est encore chaude.
+narrateur|Ils rentrent ensemble.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>porte_jardin,ballon</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,7 +1423,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Bruno veut bouger. Où joue-t-il ?</t>
+          <t>Raphaël veut bouger. Où joue-t-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1579,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Bruno veut bouger. Où joue-t-il ?</t>
+          <t>narrateur|Raphaël veut bouger.
+narrateur|Où joue-t-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1608,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Bruno a joué dehors. Papa, l'adulte, était avec lui. Les jambes ont bougé.</t>
+          <t>Raphaël a joué dehors. Papa, l'adulte, était avec lui. Les jambes ont bougé. Tu as joué dehors, avec un adulte ? Oui, papa. Dehors. Bravo, Raphaël. Tu as fait du bon travail. Le ballon rouge se repose près du bac. L'herbe a laissé une tache verte.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,7 +1752,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Bruno a joué dehors. Papa, l'adulte, était avec lui. Les jambes ont bougé.</t>
+          <t>narrateur|Raphaël a joué dehors.
+narrateur|Papa, l'adulte, était avec lui.
+narrateur|Les jambes ont bougé.
+papa|Tu as joué dehors, avec un adulte ?
+enfant-m|Oui, papa.
+enfant-m|Dehors.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|Le ballon rouge se repose près du bac.
+narrateur|L'herbe a laissé une tache verte.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1702,7 +1789,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Bruno boit de l'eau. Il sent encore l'herbe sur ses chaussures.</t>
+          <t>Papa verse un verre d'eau. Tu bois un peu d'eau ? Raphaël boit une gorgée. Il sent encore l'herbe sur ses chaussures. Merci, papa. Tu as fini de boire ? Oui. Bravo. Les miettes ne sont plus sur la table. Le pot de confiture a un couvercle.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1838,7 +1925,16 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Bruno boit de l'eau. Il sent encore l'herbe sur ses chaussures.</t>
+          <t>narrateur|Papa verse un verre d'eau.
+papa|Tu bois un peu d'eau ?
+narrateur|Raphaël boit une gorgée.
+narrateur|Il sent encore l'herbe sur ses chaussures.
+enfant-m|Merci, papa.
+papa|Tu as fini de boire ?
+enfant-m|Oui.
+papa|Bravo.
+narrateur|Les miettes ne sont plus sur la table.
+narrateur|Le pot de confiture a un couvercle.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1866,7 +1962,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai tapé le ballon. J'ai joué dehors. Avec un adulte. Bravo. C'est du bon travail. La poignée du jardin refroidit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2006,7 +2102,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai tapé le ballon.
+enfant-m|J'ai joué dehors.
+papa|Avec un adulte.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|La poignée du jardin refroidit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2028,7 +2130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2066,6 +2168,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.MOV.001-08.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-08.xlsx
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Après le goûter, Bruno a les jambes qui bougent. Papa dit : on va &lt;emphasis level="moderate"&gt;dehors&lt;/emphasis&gt;. Papa, c'est l'adulte. Ils ouvrent la porte du jardin. L'air est frais. L'herbe sent le vert. Bruno court jusqu'au ballon. Papa reste près de lui. Ils jouent dehors, avec un adulte. Bruno tape le ballon. Papa le renvoie. Les pieds tapent l'herbe. Bruno souffle. Il rit. Papa dit : encore un moment dehors. Bruno saute. Il touche les feuilles basses. Papa le voit. Ils jouent ensemble. Quand les joues de Bruno sont chaudes, papa dit : on rentre. Bruno range le ballon. Il a bougé dehors, avec un adulte.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Des miettes dorées restent sur la table. Le bois sent le gâteau. Une mouche tourne autour du pot. Le pot de confiture est collant. La poignée du jardin est chaude. Le soleil l'a touchée. Un rayon glisse sur le carrelage. Il est long, tout jaune. Raphaël vit ici, avec papa. Papa, la mouche tourne ! Oui. Elle aime le sucre. Tu as fini ton goûter ? Oui, papa. En ce moment, les jambes de Raphaël bougent. Sous la table, ses pieds tapent. Tes jambes veulent dehors ? Oui ! On va dehors, alors. On y va ensemble. On joue dehors, avec un adulte. Ils poussent la porte du jardin. L'air est frais, après le gâteau. L'herbe sent le vert. Ça sent l'herbe, papa. Oui. Tout vert. Un ballon rouge attend dans l'herbe. Il a une tache de soleil. Le ballon ! Il t'attendait. Raphaël court jusqu'au ballon. Papa reste près de lui. Je reste avec toi. Raphaël tape le ballon. Les pieds tapent l'herbe. Papa le renvoie. Bien tapé, Raphaël. Je joue dehors, avec un adulte. Oui. Bravo. Raphaël souffle un peu. Il rit. Encore un moment dehors ? Oui ! Raphaël saute. Il touche une feuille basse. La feuille est lisse et tiède. Tu vois la feuille ? Oui. Elle est douce. Ils jouent encore. Les joues de Raphaël deviennent chaudes. Tes joues sont chaudes. On rentre ? Oui, papa. Raphaël range le ballon près du bac. Une miette est encore collée à sa manche. Tu as bougé dehors, avec un adulte. Oui. Bravo. La poignée est encore chaude. Ils rentrent ensemble.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Bruno veut bouger. Où joue-t-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël veut bouger. Où joue-t-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1583,7 +1583,6 @@
 narrateur|Où joue-t-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1608,12 +1607,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a joué dehors. Papa, l'adulte, était avec lui. Les jambes ont bougé. Tu as joué dehors, avec un adulte ? Oui, papa. Dehors. Bravo, Raphaël. Tu as fait du bon travail. Le ballon rouge se repose près du bac. L'herbe a laissé une tache verte.</t>
+          <t>Raphaël a joué dehors. Papa, l'adulte, était avec lui. Les jambes ont bougé. Tu as joué dehors, avec un adulte ? Oui, papa. Dehors. Bravo, Raphaël. Le ballon rouge se repose près du bac. L'herbe a laissé une tache verte.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Bruno a joué &lt;emphasis level="moderate"&gt;dehors&lt;/emphasis&gt;. Papa, l'adulte, était avec lui. Les jambes ont bougé.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a joué dehors. Papa, l'adulte, était avec lui. Les jambes ont bougé. Tu as joué dehors, avec un adulte ? Oui, papa. Dehors. Bravo, Raphaël. Le ballon rouge se repose près du bac. L'herbe a laissé une tache verte.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1759,12 +1758,10 @@
 enfant-m|Oui, papa.
 enfant-m|Dehors.
 papa|Bravo, Raphaël.
-papa|Tu as fait du bon travail.
 narrateur|Le ballon rouge se repose près du bac.
 narrateur|L'herbe a laissé une tache verte.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1794,7 +1791,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Bruno boit de l'eau. Il sent encore l'herbe sur ses chaussures.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa verse un verre d'eau. Tu bois un peu d'eau ? Raphaël boit une gorgée. Il sent encore l'herbe sur ses chaussures. Merci, papa. Tu as fini de boire ? Oui. Bravo. Les miettes ne sont plus sur la table. Le pot de confiture a un couvercle.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1937,7 +1934,6 @@
 narrateur|Le pot de confiture a un couvercle.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1962,12 +1958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai tapé le ballon. J'ai joué dehors. Avec un adulte. Bravo. C'est du bon travail. La poignée du jardin refroidit. L'histoire est finie.</t>
+          <t>J'ai tapé le ballon. J'ai joué dehors. Avec un adulte. Bravo. La poignée du jardin refroidit.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai tapé le ballon. J'ai joué dehors. Avec un adulte. Bravo. La poignée du jardin refroidit.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2106,12 +2102,9 @@
 enfant-m|J'ai joué dehors.
 papa|Avec un adulte.
 papa|Bravo.
-papa|C'est du bon travail.
-narrateur|La poignée du jardin refroidit.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La poignée du jardin refroidit.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2130,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2175,6 +2168,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.MOV.001-08.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-08.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin</t>
+          <t>cuisine puis jardin, après le goûter</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bruno, papa</t>
+          <t>Raphaël, papa</t>
         </is>
       </c>
     </row>
